--- a/frontend/dist/template_vendor_library.xlsx
+++ b/frontend/dist/template_vendor_library.xlsx
@@ -37,7 +37,7 @@
 Cost add thêm  dành cho vendor có line ưu tiên sản xuất nhanh</t>
       </text>
     </comment>
-    <comment authorId="0" ref="D6">
+    <comment authorId="0" ref="C6">
       <text>
         <t xml:space="preserve">======
 ID#AAABeEZo3dA
@@ -57,26 +57,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
-  <si>
-    <t>bds</t>
-  </si>
-  <si>
-    <t>không tính thứ 7 và chủ nhật</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>Template Vendor mẫu</t>
   </si>
   <si>
-    <t>normal days</t>
-  </si>
-  <si>
-    <t>tính thứ 7 và chủ nhật</t>
-  </si>
-  <si>
-    <t>Ngày chạy:</t>
-  </si>
-  <si>
     <t>Thông tin chung về phôi</t>
   </si>
   <si>
@@ -86,9 +71,6 @@
     <t>Product Type</t>
   </si>
   <si>
-    <t>Ký Hiệu</t>
-  </si>
-  <si>
     <t>Hình ảnh đại diện - Video</t>
   </si>
   <si>
@@ -110,12 +92,6 @@
     <t>Link Folder</t>
   </si>
   <si>
-    <t>VN3</t>
-  </si>
-  <si>
-    <t>All-over Print Short-sleeve Hawaiian Shirt (Lightweight)</t>
-  </si>
-  <si>
     <t>Về giá</t>
   </si>
   <si>
@@ -143,6 +119,9 @@
     <t>Shipping cost: Overnight</t>
   </si>
   <si>
+    <t>Link Template</t>
+  </si>
+  <si>
     <t>Size</t>
   </si>
   <si>
@@ -153,22 +132,13 @@
   </si>
   <si>
     <t>Total Price (fulfill)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Men Hawaii </t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>M</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -205,11 +175,6 @@
       <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -268,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -290,13 +255,13 @@
     <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -308,24 +273,21 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -584,38 +546,28 @@
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
-      <c r="T1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
     </row>
     <row r="2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>4</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T2" s="1"/>
+      <c r="U2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="4" t="s">
-        <v>5</v>
-      </c>
+      <c r="D3" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -628,46 +580,47 @@
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
-      <c r="M5" s="7"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="7"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="J6" s="7"/>
+      <c r="K6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="L6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="11" t="s">
-        <v>16</v>
-      </c>
+      <c r="Q6" s="12"/>
       <c r="R6" s="12"/>
       <c r="S6" s="12"/>
       <c r="T6" s="12"/>
@@ -678,15 +631,10 @@
       <c r="Y6" s="12"/>
       <c r="Z6" s="12"/>
       <c r="AA6" s="12"/>
-      <c r="AB6" s="12"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>18</v>
-      </c>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
@@ -716,7 +664,7 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -729,7 +677,10 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="7"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="7"/>
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
@@ -746,116 +697,107 @@
     <row r="9">
       <c r="A9" s="16"/>
       <c r="B9" s="17" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="18" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="9" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="N9" s="7"/>
+      <c r="O9" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="AA9" s="14"/>
       <c r="AB9" s="14"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="10" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E10" s="19"/>
       <c r="F10" s="19"/>
       <c r="G10" s="10" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J10" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="N10" s="10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="AA10" s="20"/>
       <c r="AB10" s="20"/>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>33</v>
-      </c>
       <c r="N11" s="14"/>
       <c r="O11" s="14"/>
       <c r="AA11" s="20"/>
       <c r="AB11" s="20"/>
     </row>
     <row r="12">
-      <c r="C12" s="21" t="s">
-        <v>34</v>
-      </c>
       <c r="N12" s="14"/>
       <c r="O12" s="14"/>
     </row>
     <row r="16">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="1"/>
@@ -948,7 +890,16 @@
       <c r="P25" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
+    <mergeCell ref="D2:P2"/>
+    <mergeCell ref="D3:P3"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="A5:P5"/>
+    <mergeCell ref="A8:P8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="O9:P10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="E9:E10"/>
@@ -956,14 +907,6 @@
     <mergeCell ref="G9:H9"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="D2:P2"/>
-    <mergeCell ref="D3:P3"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="A8:M8"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
